--- a/data/external/safety_lines/2026-W32.xlsx
+++ b/data/external/safety_lines/2026-W32.xlsx
@@ -417,18 +417,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,25 +456,35 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>valid_from</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>valid_to</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>d7_cpi_ceiling</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>d7_roas_floor</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>d1_retention_floor</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>daily_budget_cap</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>updated_by</t>
         </is>
@@ -499,19 +511,29 @@
           <t>2026-W32</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>2.2</v>
       </c>
-      <c r="F2" t="n">
+      <c r="H2" t="n">
         <v>0.42</v>
       </c>
-      <c r="G2" t="n">
+      <c r="I2" t="n">
         <v>0.319</v>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
         <v>3000</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>ua_ops</t>
         </is>
@@ -538,19 +560,29 @@
           <t>2026-W32</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
         <v>1.94</v>
       </c>
-      <c r="F3" t="n">
+      <c r="H3" t="n">
         <v>0.448</v>
       </c>
-      <c r="G3" t="n">
+      <c r="I3" t="n">
         <v>0.321</v>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="n">
         <v>2600</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>ua_ops</t>
         </is>
@@ -577,19 +609,29 @@
           <t>2026-W32</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
         <v>1.8</v>
       </c>
-      <c r="F4" t="n">
+      <c r="H4" t="n">
         <v>0.464</v>
       </c>
-      <c r="G4" t="n">
+      <c r="I4" t="n">
         <v>0.322</v>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
         <v>2400</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>ua_ops</t>
         </is>
@@ -616,19 +658,29 @@
           <t>2026-W32</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
         <v>2.97</v>
       </c>
-      <c r="F5" t="n">
+      <c r="H5" t="n">
         <v>0.361</v>
       </c>
-      <c r="G5" t="n">
+      <c r="I5" t="n">
         <v>0.314</v>
       </c>
-      <c r="H5" t="n">
+      <c r="J5" t="n">
         <v>4000</v>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>ua_ops</t>
         </is>
@@ -655,19 +707,29 @@
           <t>2026-W32</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
         <v>0.77</v>
       </c>
-      <c r="F6" t="n">
+      <c r="H6" t="n">
         <v>0.71</v>
       </c>
-      <c r="G6" t="n">
+      <c r="I6" t="n">
         <v>0.331</v>
       </c>
-      <c r="H6" t="n">
+      <c r="J6" t="n">
         <v>1000</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>ua_ops</t>
         </is>
@@ -694,19 +756,29 @@
           <t>2026-W32</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
         <v>1.76</v>
       </c>
-      <c r="F7" t="n">
+      <c r="H7" t="n">
         <v>0.47</v>
       </c>
-      <c r="G7" t="n">
+      <c r="I7" t="n">
         <v>0.322</v>
       </c>
-      <c r="H7" t="n">
+      <c r="J7" t="n">
         <v>2400</v>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>ua_ops</t>
         </is>
@@ -733,19 +805,29 @@
           <t>2026-W32</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
         <v>1.55</v>
       </c>
-      <c r="F8" t="n">
+      <c r="H8" t="n">
         <v>0.501</v>
       </c>
-      <c r="G8" t="n">
+      <c r="I8" t="n">
         <v>0.324</v>
       </c>
-      <c r="H8" t="n">
+      <c r="J8" t="n">
         <v>2100</v>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>ua_ops</t>
         </is>
@@ -772,19 +854,29 @@
           <t>2026-W32</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
         <v>1.44</v>
       </c>
-      <c r="F9" t="n">
+      <c r="H9" t="n">
         <v>0.519</v>
       </c>
-      <c r="G9" t="n">
+      <c r="I9" t="n">
         <v>0.325</v>
       </c>
-      <c r="H9" t="n">
+      <c r="J9" t="n">
         <v>1900</v>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>ua_ops</t>
         </is>
@@ -811,19 +903,29 @@
           <t>2026-W32</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
         <v>2.38</v>
       </c>
-      <c r="F10" t="n">
+      <c r="H10" t="n">
         <v>0.404</v>
       </c>
-      <c r="G10" t="n">
+      <c r="I10" t="n">
         <v>0.318</v>
       </c>
-      <c r="H10" t="n">
+      <c r="J10" t="n">
         <v>3200</v>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>ua_ops</t>
         </is>
@@ -850,19 +952,29 @@
           <t>2026-W32</t>
         </is>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
         <v>0.62</v>
       </c>
-      <c r="F11" t="n">
+      <c r="H11" t="n">
         <v>0.794</v>
       </c>
-      <c r="G11" t="n">
+      <c r="I11" t="n">
         <v>0.333</v>
       </c>
-      <c r="H11" t="n">
+      <c r="J11" t="n">
         <v>800</v>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>ua_ops</t>
         </is>
@@ -889,19 +1001,29 @@
           <t>2026-W32</t>
         </is>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
         <v>4.07</v>
       </c>
-      <c r="F12" t="n">
+      <c r="H12" t="n">
         <v>0.309</v>
       </c>
-      <c r="G12" t="n">
+      <c r="I12" t="n">
         <v>0.309</v>
       </c>
-      <c r="H12" t="n">
+      <c r="J12" t="n">
         <v>5500</v>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>ua_ops</t>
         </is>
@@ -928,19 +1050,29 @@
           <t>2026-W32</t>
         </is>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
         <v>3.58</v>
       </c>
-      <c r="F13" t="n">
+      <c r="H13" t="n">
         <v>0.329</v>
       </c>
-      <c r="G13" t="n">
+      <c r="I13" t="n">
         <v>0.311</v>
       </c>
-      <c r="H13" t="n">
+      <c r="J13" t="n">
         <v>4800</v>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>ua_ops</t>
         </is>
@@ -967,19 +1099,29 @@
           <t>2026-W32</t>
         </is>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
         <v>3.34</v>
       </c>
-      <c r="F14" t="n">
+      <c r="H14" t="n">
         <v>0.341</v>
       </c>
-      <c r="G14" t="n">
+      <c r="I14" t="n">
         <v>0.312</v>
       </c>
-      <c r="H14" t="n">
+      <c r="J14" t="n">
         <v>4500</v>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>ua_ops</t>
         </is>
@@ -1006,19 +1148,29 @@
           <t>2026-W32</t>
         </is>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
         <v>5.49</v>
       </c>
-      <c r="F15" t="n">
+      <c r="H15" t="n">
         <v>0.266</v>
       </c>
-      <c r="G15" t="n">
+      <c r="I15" t="n">
         <v>0.302</v>
       </c>
-      <c r="H15" t="n">
+      <c r="J15" t="n">
         <v>7400</v>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>ua_ops</t>
         </is>
@@ -1045,19 +1197,29 @@
           <t>2026-W32</t>
         </is>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
         <v>1.42</v>
       </c>
-      <c r="F16" t="n">
+      <c r="H16" t="n">
         <v>0.522</v>
       </c>
-      <c r="G16" t="n">
+      <c r="I16" t="n">
         <v>0.325</v>
       </c>
-      <c r="H16" t="n">
+      <c r="J16" t="n">
         <v>1900</v>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>ua_ops</t>
         </is>
@@ -1084,19 +1246,29 @@
           <t>2026-W32</t>
         </is>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
         <v>0.99</v>
       </c>
-      <c r="F17" t="n">
+      <c r="H17" t="n">
         <v>0.626</v>
       </c>
-      <c r="G17" t="n">
+      <c r="I17" t="n">
         <v>0.329</v>
       </c>
-      <c r="H17" t="n">
+      <c r="J17" t="n">
         <v>1300</v>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>ua_ops</t>
         </is>
@@ -1123,19 +1295,29 @@
           <t>2026-W32</t>
         </is>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
         <v>0.87</v>
       </c>
-      <c r="F18" t="n">
+      <c r="H18" t="n">
         <v>0.667</v>
       </c>
-      <c r="G18" t="n">
+      <c r="I18" t="n">
         <v>0.33</v>
       </c>
-      <c r="H18" t="n">
+      <c r="J18" t="n">
         <v>1100</v>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>ua_ops</t>
         </is>
@@ -1162,19 +1344,29 @@
           <t>2026-W32</t>
         </is>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="F19" t="n">
+      <c r="H19" t="n">
         <v>0.6909999999999999</v>
       </c>
-      <c r="G19" t="n">
+      <c r="I19" t="n">
         <v>0.331</v>
       </c>
-      <c r="H19" t="n">
+      <c r="J19" t="n">
         <v>1100</v>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>ua_ops</t>
         </is>
@@ -1201,19 +1393,29 @@
           <t>2026-W32</t>
         </is>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
         <v>1.34</v>
       </c>
-      <c r="F20" t="n">
+      <c r="H20" t="n">
         <v>0.539</v>
       </c>
-      <c r="G20" t="n">
+      <c r="I20" t="n">
         <v>0.326</v>
       </c>
-      <c r="H20" t="n">
+      <c r="J20" t="n">
         <v>1800</v>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>ua_ops</t>
         </is>
@@ -1240,19 +1442,29 @@
           <t>2026-W32</t>
         </is>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
         <v>0.35</v>
       </c>
-      <c r="F21" t="n">
+      <c r="H21" t="n">
         <v>1.058</v>
       </c>
-      <c r="G21" t="n">
+      <c r="I21" t="n">
         <v>0.336</v>
       </c>
-      <c r="H21" t="n">
+      <c r="J21" t="n">
         <v>400</v>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>ua_ops</t>
         </is>
@@ -1279,19 +1491,29 @@
           <t>2026-W32</t>
         </is>
       </c>
-      <c r="E22" t="n">
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
         <v>3.52</v>
       </c>
-      <c r="F22" t="n">
+      <c r="H22" t="n">
         <v>0.332</v>
       </c>
-      <c r="G22" t="n">
+      <c r="I22" t="n">
         <v>0.311</v>
       </c>
-      <c r="H22" t="n">
+      <c r="J22" t="n">
         <v>4800</v>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>ua_ops</t>
         </is>
@@ -1318,19 +1540,29 @@
           <t>2026-W32</t>
         </is>
       </c>
-      <c r="E23" t="n">
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
         <v>3.1</v>
       </c>
-      <c r="F23" t="n">
+      <c r="H23" t="n">
         <v>0.354</v>
       </c>
-      <c r="G23" t="n">
+      <c r="I23" t="n">
         <v>0.314</v>
       </c>
-      <c r="H23" t="n">
+      <c r="J23" t="n">
         <v>4200</v>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>ua_ops</t>
         </is>
@@ -1357,19 +1589,29 @@
           <t>2026-W32</t>
         </is>
       </c>
-      <c r="E24" t="n">
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
         <v>2.89</v>
       </c>
-      <c r="F24" t="n">
+      <c r="H24" t="n">
         <v>0.367</v>
       </c>
-      <c r="G24" t="n">
+      <c r="I24" t="n">
         <v>0.315</v>
       </c>
-      <c r="H24" t="n">
+      <c r="J24" t="n">
         <v>3900</v>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>ua_ops</t>
         </is>
@@ -1396,19 +1638,29 @@
           <t>2026-W32</t>
         </is>
       </c>
-      <c r="E25" t="n">
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
         <v>4.75</v>
       </c>
-      <c r="F25" t="n">
+      <c r="H25" t="n">
         <v>0.286</v>
       </c>
-      <c r="G25" t="n">
+      <c r="I25" t="n">
         <v>0.305</v>
       </c>
-      <c r="H25" t="n">
+      <c r="J25" t="n">
         <v>6400</v>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>ua_ops</t>
         </is>
@@ -1435,19 +1687,29 @@
           <t>2026-W32</t>
         </is>
       </c>
-      <c r="E26" t="n">
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
         <v>1.23</v>
       </c>
-      <c r="F26" t="n">
+      <c r="H26" t="n">
         <v>0.5610000000000001</v>
       </c>
-      <c r="G26" t="n">
+      <c r="I26" t="n">
         <v>0.327</v>
       </c>
-      <c r="H26" t="n">
+      <c r="J26" t="n">
         <v>1600</v>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>ua_ops</t>
         </is>
